--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xiaoc\Documents\MMUser\config\becExpConfig\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scientist\Documents\MMUser\config\becExpConfig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E773D7-F5FF-4BC2-A747-95181897BBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E033CF1-9311-4742-B647-EDF0FD9DCFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>TOF</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,23 +50,35 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>t_image</t>
+  </si>
+  <si>
+    <t>\mu s</t>
+  </si>
+  <si>
+    <t>RM2Hi</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -80,7 +92,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,15 +100,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -374,15 +388,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.73046875" customWidth="1"/>
-    <col min="2" max="2" width="21.59765625" customWidth="1"/>
-    <col min="3" max="4" width="12.265625" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="true"/>
+    <col min="2" max="2" width="21.5703125" customWidth="true"/>
+    <col min="3" max="4" width="12.28515625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -390,7 +404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -398,17 +412,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="142">
   <si>
     <t>cMOT_tot</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -492,6 +492,18 @@
   </si>
   <si>
     <t>Hz</t>
+  </si>
+  <si>
+    <t>hw_ImagingPci</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>rfknifeend</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
 </sst>
 </file>
@@ -818,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="true"/>
@@ -1538,6 +1550,22 @@
         <v>137</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="150">
   <si>
     <t>cMOT_tot</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -501,6 +501,30 @@
   </si>
   <si>
     <t>rfknifeend</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_SpModDepth</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_PfModDepth</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_SdModDepth</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth2</t>
   </si>
   <si>
     <t>V</t>
@@ -830,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="true"/>
@@ -1566,6 +1590,38 @@
         <v>141</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="156">
   <si>
     <t>cMOT_tot</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -525,6 +525,24 @@
   </si>
   <si>
     <t>hw_PdModDepth2</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>FeshbachField3</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_XvNiCC</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_XvLatticeCC</t>
   </si>
   <si>
     <t>V</t>
@@ -854,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="true"/>
@@ -1622,6 +1640,30 @@
         <v>149</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scientist\Documents\MMUser\config\becExpConfig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E033CF1-9311-4742-B647-EDF0FD9DCFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F643081-E629-4DFE-9001-B841175414E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="true"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>TOF</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,6 +59,69 @@
   </si>
   <si>
     <t>RM2Hi</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>XODTEvapEnd</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Lattice1EvapEnd</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>LatticeHold</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>DummyIndex</t>
+  </si>
+  <si>
+    <t>RedFreqDuringMTLoad</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>RedVVADuringMTLoad</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>XODTRampDownEnd</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>LoadMT</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>BlueMOTP10</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>LatticeRamp</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>EvapShakenTrap</t>
   </si>
   <si>
     <t>V</t>
@@ -92,7 +155,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -100,14 +163,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,15 +449,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="true"/>
-    <col min="2" max="2" width="21.5703125" customWidth="true"/>
-    <col min="3" max="4" width="12.28515625" customWidth="true"/>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="4" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -404,7 +465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -412,12 +473,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -425,7 +486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -433,12 +494,97 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="168">
   <si>
     <t>cMOT_tot</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -543,6 +543,42 @@
   </si>
   <si>
     <t>hw_XvLatticeCC</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_PdModDepthP1</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_PdModDepthP5</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>curveField3</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_XvGw</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_StirapModDepth</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_EitModDepth</t>
   </si>
   <si>
     <t>V</t>
@@ -872,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="true"/>
@@ -1664,6 +1700,54 @@
         <v>155</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F643081-E629-4DFE-9001-B841175414E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>TOF</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,6 +122,99 @@
   </si>
   <si>
     <t>EvapShakenTrap</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>RM3ShakenTrap</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>BECHold</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>hw_RampTime</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>RampTime</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>hw_ShakeFreq</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>hw_ShakeFrequency</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>hw_EnvDuration</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>MaxShake</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>holdTime_us</t>
+  </si>
+  <si>
+    <t>\mu s</t>
+  </si>
+  <si>
+    <t>Lattice1Max</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>RM3ModEnd</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>ShakenTrapVVA</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>RedMOT1Offset</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>RedMOT1Max</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>RedMOT1Min</t>
   </si>
   <si>
     <t>V</t>
@@ -155,7 +248,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -163,12 +256,14 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,15 +544,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="4" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" customWidth="true"/>
+    <col min="2" max="2" width="21.5703125" customWidth="true"/>
+    <col min="3" max="4" width="12.28515625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -465,7 +560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -473,12 +568,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -486,7 +581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -494,7 +589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -502,7 +597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -510,7 +605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -518,7 +613,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -526,12 +621,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -539,7 +634,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -547,7 +642,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -555,7 +650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -563,7 +658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -571,7 +666,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -579,12 +674,138 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17">
       <c r="A17" t="s">
         <v>30</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="176">
   <si>
     <t>cMOT_tot</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -582,6 +582,30 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>hw_GWFreq</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>hw_SPDModDepth</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_DgModDepth</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_SPDfrequency</t>
+  </si>
+  <si>
+    <t>Hz</t>
   </si>
 </sst>
 </file>
@@ -908,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="true"/>
@@ -1748,6 +1772,38 @@
         <v>167</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>TOF</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -218,6 +218,21 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>LoadMT</t>
+  </si>
+  <si>
+    <t>RepumpFlash</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>MTHold</t>
+  </si>
+  <si>
+    <t>ms</t>
   </si>
 </sst>
 </file>
@@ -544,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.28515625" customWidth="true"/>
@@ -808,6 +823,28 @@
         <v>62</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="0"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/becExpConfig/parameterUnit.csv.xlsx
+++ b/config/becExpConfig/parameterUnit.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="190">
   <si>
     <t>cMOT_tot</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -606,6 +606,48 @@
   </si>
   <si>
     <t>Hz</t>
+  </si>
+  <si>
+    <t>hw_SDModDepth</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>hw_GWFreqOffset</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>GWwHoldTime</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>GwHoldTime</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>hw_GWPhase</t>
+  </si>
+  <si>
+    <t>rad</t>
+  </si>
+  <si>
+    <t>hw_GWModDepth</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>bouncehold</t>
+  </si>
+  <si>
+    <t>ms</t>
   </si>
 </sst>
 </file>
@@ -932,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="true"/>
@@ -1804,6 +1846,62 @@
         <v>175</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
